--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-transferkoeffizient.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-transferkoeffizient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5905" uniqueCount="665">
   <si>
     <t>Property</t>
   </si>
@@ -866,7 +866,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:code}
 </t>
   </si>
   <si>
@@ -1747,6 +1747,13 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="component:&amp;lt;slice&amp;gt;.code"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -1865,6 +1872,10 @@
   </si>
   <si>
     <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>Observation.component:predicted.code.coding:sct</t>
@@ -12832,7 +12843,7 @@
         <v>81</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>81</v>
+        <v>554</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>81</v>
@@ -12890,7 +12901,7 @@
         <v>81</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>81</v>
@@ -12901,10 +12912,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13016,10 +13027,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13133,10 +13144,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13252,10 +13263,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13281,13 +13292,13 @@
         <v>232</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>261</v>
@@ -13339,7 +13350,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>91</v>
@@ -13357,7 +13368,7 @@
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>266</v>
@@ -13371,10 +13382,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13397,16 +13408,16 @@
         <v>92</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O94" t="s" s="2">
         <v>386</v>
@@ -13458,7 +13469,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13476,7 +13487,7 @@
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>389</v>
@@ -13490,10 +13501,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13519,13 +13530,13 @@
         <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>434</v>
@@ -13577,7 +13588,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13609,10 +13620,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13638,10 +13649,10 @@
         <v>232</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>443</v>
@@ -13696,7 +13707,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13728,10 +13739,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13757,10 +13768,10 @@
         <v>82</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>494</v>
@@ -13815,7 +13826,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13847,13 +13858,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>549</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>81</v>
@@ -13878,10 +13889,10 @@
         <v>491</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>552</v>
@@ -13957,7 +13968,7 @@
         <v>81</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>81</v>
@@ -13968,10 +13979,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14083,10 +14094,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14200,10 +14211,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14319,10 +14330,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14348,13 +14359,13 @@
         <v>232</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>261</v>
@@ -14406,7 +14417,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>91</v>
@@ -14424,7 +14435,7 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>266</v>
@@ -14438,10 +14449,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14553,10 +14564,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14670,10 +14681,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14745,7 +14756,7 @@
         <v>81</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>272</v>
+        <v>594</v>
       </c>
       <c r="AC105" s="2"/>
       <c r="AD105" t="s" s="2">
@@ -14787,10 +14798,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>309</v>
@@ -14906,10 +14917,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>321</v>
@@ -15025,10 +15036,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15144,10 +15155,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15170,16 +15181,16 @@
         <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O109" t="s" s="2">
         <v>386</v>
@@ -15219,7 +15230,7 @@
         <v>81</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AC109" s="2"/>
       <c r="AD109" t="s" s="2">
@@ -15229,7 +15240,7 @@
         <v>117</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15247,7 +15258,7 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>389</v>
@@ -15261,13 +15272,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>81</v>
@@ -15292,13 +15303,13 @@
         <v>382</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O110" t="s" s="2">
         <v>386</v>
@@ -15350,7 +15361,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15368,7 +15379,7 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>389</v>
@@ -15382,10 +15393,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15497,10 +15508,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15614,10 +15625,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15733,10 +15744,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15852,10 +15863,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15969,10 +15980,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16086,10 +16097,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16205,10 +16216,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16234,13 +16245,13 @@
         <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O118" t="s" s="2">
         <v>434</v>
@@ -16292,7 +16303,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16324,10 +16335,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16353,10 +16364,10 @@
         <v>232</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>443</v>
@@ -16411,7 +16422,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16443,10 +16454,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16472,10 +16483,10 @@
         <v>82</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>494</v>
@@ -16530,7 +16541,7 @@
         <v>81</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16562,13 +16573,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>549</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>81</v>
@@ -16593,10 +16604,10 @@
         <v>491</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>552</v>
@@ -16672,7 +16683,7 @@
         <v>81</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>81</v>
@@ -16683,10 +16694,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16798,10 +16809,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16915,10 +16926,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17034,10 +17045,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17063,13 +17074,13 @@
         <v>232</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>261</v>
@@ -17121,7 +17132,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>91</v>
@@ -17139,7 +17150,7 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>266</v>
@@ -17153,10 +17164,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17268,10 +17279,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17385,10 +17396,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17460,7 +17471,7 @@
         <v>81</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>272</v>
+        <v>594</v>
       </c>
       <c r="AC128" s="2"/>
       <c r="AD128" t="s" s="2">
@@ -17502,10 +17513,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>309</v>
@@ -17621,10 +17632,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>321</v>
@@ -17740,10 +17751,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17859,10 +17870,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17885,16 +17896,16 @@
         <v>92</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O132" t="s" s="2">
         <v>386</v>
@@ -17934,7 +17945,7 @@
         <v>81</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AC132" s="2"/>
       <c r="AD132" t="s" s="2">
@@ -17944,7 +17955,7 @@
         <v>117</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17962,7 +17973,7 @@
         <v>81</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>389</v>
@@ -17976,13 +17987,13 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D133" t="s" s="2">
         <v>81</v>
@@ -18007,13 +18018,13 @@
         <v>382</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O133" t="s" s="2">
         <v>386</v>
@@ -18065,7 +18076,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18083,7 +18094,7 @@
         <v>81</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>389</v>
@@ -18097,10 +18108,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18212,10 +18223,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18329,10 +18340,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18448,10 +18459,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18567,10 +18578,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18613,7 +18624,7 @@
         <v>81</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>81</v>
@@ -18684,10 +18695,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18801,10 +18812,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18849,7 +18860,7 @@
         <v>81</v>
       </c>
       <c r="S140" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="T140" t="s" s="2">
         <v>81</v>
@@ -18920,10 +18931,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18949,13 +18960,13 @@
         <v>232</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O141" t="s" s="2">
         <v>434</v>
@@ -19007,7 +19018,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19039,10 +19050,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19068,10 +19079,10 @@
         <v>232</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>443</v>
@@ -19126,7 +19137,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19158,10 +19169,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19187,10 +19198,10 @@
         <v>82</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>494</v>
@@ -19245,7 +19256,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19277,13 +19288,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>549</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>81</v>
@@ -19308,10 +19319,10 @@
         <v>491</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>552</v>
@@ -19387,7 +19398,7 @@
         <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>81</v>
@@ -19398,10 +19409,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19513,10 +19524,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19630,10 +19641,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19749,10 +19760,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19778,13 +19789,13 @@
         <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O148" t="s" s="2">
         <v>261</v>
@@ -19836,7 +19847,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>91</v>
@@ -19854,7 +19865,7 @@
         <v>81</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>266</v>
@@ -19868,10 +19879,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19983,10 +19994,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20100,10 +20111,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20175,7 +20186,7 @@
         <v>81</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>272</v>
+        <v>594</v>
       </c>
       <c r="AC151" s="2"/>
       <c r="AD151" t="s" s="2">
@@ -20217,10 +20228,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>309</v>
@@ -20267,7 +20278,7 @@
         <v>81</v>
       </c>
       <c r="S152" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="T152" t="s" s="2">
         <v>81</v>
@@ -20336,10 +20347,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20455,10 +20466,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20481,16 +20492,16 @@
         <v>92</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O154" t="s" s="2">
         <v>386</v>
@@ -20542,7 +20553,7 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20560,7 +20571,7 @@
         <v>81</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM154" t="s" s="2">
         <v>389</v>
@@ -20574,10 +20585,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20603,13 +20614,13 @@
         <v>232</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O155" t="s" s="2">
         <v>434</v>
@@ -20661,7 +20672,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -20693,10 +20704,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20722,10 +20733,10 @@
         <v>232</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N156" t="s" s="2">
         <v>443</v>
@@ -20780,7 +20791,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -20812,10 +20823,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20841,10 +20852,10 @@
         <v>82</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N157" t="s" s="2">
         <v>494</v>
@@ -20899,7 +20910,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
